--- a/output/京都滋賀_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/京都滋賀_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
